--- a/src/assets/intakePack/CommercialIndustrialFinanceIntakeWorkbookMOCKDATA.xlsx
+++ b/src/assets/intakePack/CommercialIndustrialFinanceIntakeWorkbookMOCKDATA.xlsx
@@ -888,7 +888,7 @@
     <x:t xml:space="preserve">The information recorded in this pack has been provided by the client and is, to the best of their knowledge, accurate at the date below. It will be verified against source documents before any finance application is made.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The client consents to Naidu Property Consulting Services collecting, holding and using the information in this pack for the purpose of assessing and, if instructed, arranging commercial or industrial finance, and to it being disclosed to prospective lenders, valuers, insurers and professional advisers engaged for that purpose.</x:t>
+    <x:t xml:space="preserve">The client consents to Meridian Commercial Advisory collecting, holding and using the information in this pack for the purpose of assessing and, if instructed, arranging commercial or industrial finance, and to it being disclosed to prospective lenders, valuers, insurers and professional advisers engaged for that purpose.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Client name</x:t>
@@ -2132,7 +2132,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C40" s="122" t="str">
-        <x:v>Naidu Property Consulting Services</x:v>
+        <x:v>Meridian Commercial Advisory</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2140,7 +2140,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="123" t="str">
-        <x:v>www.npcservices.com.au</x:v>
+        <x:v>www.meridiancommercial.example</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2148,7 +2148,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="123" t="str">
-        <x:v>property@npcservices.com.au</x:v>
+        <x:v>advisory@meridiancommercial.example</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2156,7 +2156,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C43" s="123" t="str">
-        <x:v>03 9000 0000 (mock)</x:v>
+        <x:v>03 9000 4417 (mock)</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2164,7 +2164,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="C44" s="123" t="str">
-        <x:v>Level 8, 123 Collins Street, Melbourne VIC 3000 (mock)</x:v>
+        <x:v>Level 12, 45 Sturt Street, Southbank VIC 3006 (mock)</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2172,7 +2172,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C45" s="123" t="str">
-        <x:v>25 689 472 311 (fictional test identifier)</x:v>
+        <x:v>47 002 615 900 (fictional test identifier)</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" customHeight="1">
@@ -2698,7 +2698,7 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="B7" s="135" t="str">
-        <x:v>Maya Collins, Naidu Property Consulting Services, is coordinating the fact-find and lender submission.</x:v>
+        <x:v>Maya Collins, Meridian Commercial Advisory, is coordinating the fact-find and lender submission.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="s">
         <x:v>120</x:v>
